--- a/analysis/econometrics_outputs/contdid/Graficos/contracts/dose/contdid_rf_dose_att.xlsx
+++ b/analysis/econometrics_outputs/contdid/Graficos/contracts/dose/contdid_rf_dose_att.xlsx
@@ -488,10 +488,10 @@
         <v>-631.232936843879</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>676.546367454891</v>
+        <v>624.533841719459</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H6" s="1"/>
       <c r="I6" s="1"/>
@@ -510,10 +510,10 @@
         <v>-591.221320697499</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>666.988572269426</v>
+        <v>579.198625403236</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H7" s="1"/>
       <c r="I7" s="1"/>
@@ -532,10 +532,10 @@
         <v>-533.402305344283</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>656.404229636767</v>
+        <v>527.097122230585</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H8" s="1"/>
       <c r="I8" s="1"/>
@@ -554,10 +554,10 @@
         <v>-499.518564335781</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>649.732393295023</v>
+        <v>474.085122991674</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H9" s="1"/>
       <c r="I9" s="1"/>
@@ -576,10 +576,10 @@
         <v>-433.471682781005</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>635.613144069591</v>
+        <v>385.801453053694</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H10" s="1"/>
       <c r="I10" s="1"/>
@@ -598,10 +598,10 @@
         <v>-403.576513524971</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>608.023822363282</v>
+        <v>379.292417090841</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="1"/>
@@ -620,10 +620,10 @@
         <v>-389.502601425882</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>585.871584824905</v>
+        <v>367.393320620774</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H12" s="1"/>
       <c r="I12" s="1"/>
@@ -642,10 +642,10 @@
         <v>-373.685895906696</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>561.203494842068</v>
+        <v>333.916101963765</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H13" s="1"/>
       <c r="I13" s="1"/>
@@ -664,10 +664,10 @@
         <v>-361.135466657741</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>541.807078923057</v>
+        <v>346.667235822056</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
@@ -686,10 +686,10 @@
         <v>-330.527566753075</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>495.197457610498</v>
+        <v>340.371303892538</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
@@ -708,10 +708,10 @@
         <v>-309.723906980057</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>464.114049405197</v>
+        <v>299.788915529887</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -730,10 +730,10 @@
         <v>-279.030817355731</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>419.208720608126</v>
+        <v>306.685786210081</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H17" s="1"/>
       <c r="I17" s="1"/>
@@ -752,10 +752,10 @@
         <v>-260.268702412121</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>392.360665158589</v>
+        <v>295.7477944765</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H18" s="1"/>
       <c r="I18" s="1"/>
@@ -774,10 +774,10 @@
         <v>-249.957349512162</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>377.812528161412</v>
+        <v>279.96287326258</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H19" s="1"/>
       <c r="I19" s="1"/>
@@ -796,10 +796,10 @@
         <v>-232.498724620444</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>353.533145663999</v>
+        <v>297.416328630826</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
@@ -818,10 +818,10 @@
         <v>-190.168288716451</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>296.66570120942</v>
+        <v>288.268847818231</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H21" s="1"/>
       <c r="I21" s="1"/>
@@ -840,10 +840,10 @@
         <v>-176.70180499179</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>279.224766467688</v>
+        <v>295.551526815205</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H22" s="1"/>
       <c r="I22" s="1"/>
@@ -862,10 +862,10 @@
         <v>-157.670807076383</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>270.975298450449</v>
+        <v>275.575792608255</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H23" s="1"/>
       <c r="I23" s="1"/>
@@ -884,10 +884,10 @@
         <v>-139.668583360522</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>264.139996622489</v>
+        <v>276.601739354412</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H24" s="1"/>
       <c r="I24" s="1"/>
@@ -906,10 +906,10 @@
         <v>-125.673082351362</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>240.82695530016</v>
+        <v>276.401521425456</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H25" s="1"/>
       <c r="I25" s="1"/>
@@ -928,10 +928,10 @@
         <v>-108.752159132185</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>213.012183917433</v>
+        <v>277.862863836726</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H26" s="1"/>
       <c r="I26" s="1"/>
@@ -950,10 +950,10 @@
         <v>-94.3976210870146</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>189.757546584815</v>
+        <v>283.675394537025</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
@@ -972,10 +972,10 @@
         <v>-75.7861686507755</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>161.019617070789</v>
+        <v>276.552987636883</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H28" s="1"/>
       <c r="I28" s="1"/>
@@ -994,10 +994,10 @@
         <v>-53.0263275792046</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>138.158393317742</v>
+        <v>261.839064044304</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H29" s="1"/>
       <c r="I29" s="1"/>
@@ -1016,10 +1016,10 @@
         <v>-47.5974530063282</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>132.963244031837</v>
+        <v>257.947666142254</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -1038,10 +1038,10 @@
         <v>-22.7912082450114</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>110.633744243875</v>
+        <v>241.288821053653</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -1060,10 +1060,10 @@
         <v>-16.8566957845834</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>105.662258396331</v>
+        <v>239.987590569829</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H32" s="1"/>
       <c r="I32" s="1"/>
@@ -1082,10 +1082,10 @@
         <v>-11.0479432681133</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>100.946389188134</v>
+        <v>238.60166315256</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H33" s="1"/>
       <c r="I33" s="1"/>
@@ -1104,10 +1104,10 @@
         <v>4.37606237176768</v>
       </c>
       <c r="F34" s="1" t="n">
-        <v>89.1938024161426</v>
+        <v>233.43920520456</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1"/>
@@ -1126,10 +1126,10 @@
         <v>13.0126963669516</v>
       </c>
       <c r="F35" s="1" t="n">
-        <v>83.1382357628825</v>
+        <v>231.559907246696</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H35" s="1"/>
       <c r="I35" s="1"/>
@@ -1148,10 +1148,10 @@
         <v>19.6167858671787</v>
       </c>
       <c r="F36" s="1" t="n">
-        <v>78.7825637129709</v>
+        <v>231.2935725977</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H36" s="1"/>
       <c r="I36" s="1"/>
@@ -1170,10 +1170,10 @@
         <v>36.5516752777791</v>
       </c>
       <c r="F37" s="1" t="n">
-        <v>71.576322971519</v>
+        <v>234.05878043013</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H37" s="1"/>
       <c r="I37" s="1"/>
@@ -1192,10 +1192,10 @@
         <v>44.1568096423275</v>
       </c>
       <c r="F38" s="1" t="n">
-        <v>77.4014126368432</v>
+        <v>234.646713605124</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H38" s="1"/>
       <c r="I38" s="1"/>
@@ -1214,10 +1214,10 @@
         <v>55.9574248311091</v>
       </c>
       <c r="F39" s="1" t="n">
-        <v>86.8210796828726</v>
+        <v>237.082595191906</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H39" s="1"/>
       <c r="I39" s="1"/>
@@ -1236,10 +1236,10 @@
         <v>64.2669715680079</v>
       </c>
       <c r="F40" s="1" t="n">
-        <v>93.7609403257915</v>
+        <v>241.402863368796</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H40" s="1"/>
       <c r="I40" s="1"/>
@@ -1258,10 +1258,10 @@
         <v>69.2122366982558</v>
       </c>
       <c r="F41" s="1" t="n">
-        <v>98.0229036007956</v>
+        <v>242.290178913543</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
@@ -1280,10 +1280,10 @@
         <v>76.6948417817543</v>
       </c>
       <c r="F42" s="1" t="n">
-        <v>104.673632933063</v>
+        <v>237.863344292053</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
@@ -1302,10 +1302,10 @@
         <v>103.869028314035</v>
       </c>
       <c r="F43" s="1" t="n">
-        <v>131.194713654323</v>
+        <v>243.507865254261</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H43" s="1"/>
       <c r="I43" s="1"/>
@@ -1324,10 +1324,10 @@
         <v>108.511795610644</v>
       </c>
       <c r="F44" s="1" t="n">
-        <v>136.146376809472</v>
+        <v>237.926630969779</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H44" s="1"/>
       <c r="I44" s="1"/>
@@ -1346,10 +1346,10 @@
         <v>111.241547831691</v>
       </c>
       <c r="F45" s="1" t="n">
-        <v>139.119338767269</v>
+        <v>232.339291971862</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H45" s="1"/>
       <c r="I45" s="1"/>
@@ -1368,10 +1368,10 @@
         <v>126.01236152874</v>
       </c>
       <c r="F46" s="1" t="n">
-        <v>155.97429710411</v>
+        <v>248.337886987437</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
@@ -1390,10 +1390,10 @@
         <v>131.163156930879</v>
       </c>
       <c r="F47" s="1" t="n">
-        <v>162.123473140929</v>
+        <v>236.906863047005</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H47" s="1"/>
       <c r="I47" s="1"/>
@@ -1412,10 +1412,10 @@
         <v>134.810857232579</v>
       </c>
       <c r="F48" s="1" t="n">
-        <v>166.565691732432</v>
+        <v>222.958506780965</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H48" s="1"/>
       <c r="I48" s="1"/>
@@ -1434,10 +1434,10 @@
         <v>144.048849265598</v>
       </c>
       <c r="F49" s="1" t="n">
-        <v>178.230682362237</v>
+        <v>221.994602029116</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -1456,10 +1456,10 @@
         <v>146.000832172333</v>
       </c>
       <c r="F50" s="1" t="n">
-        <v>180.791366600924</v>
+        <v>219.089613517522</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H50" s="1"/>
       <c r="I50" s="1"/>
@@ -1478,10 +1478,10 @@
         <v>153.504010525789</v>
       </c>
       <c r="F51" s="1" t="n">
-        <v>188.438955269821</v>
+        <v>224.918879487245</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H51" s="1"/>
       <c r="I51" s="1"/>
@@ -1500,10 +1500,10 @@
         <v>154.586136616716</v>
       </c>
       <c r="F52" s="1" t="n">
-        <v>187.524945109828</v>
+        <v>225.693003511998</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
@@ -1522,10 +1522,10 @@
         <v>158.538139213744</v>
       </c>
       <c r="F53" s="1" t="n">
-        <v>183.815080010458</v>
+        <v>235.016352391579</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
@@ -1544,10 +1544,10 @@
         <v>159.21872477108</v>
       </c>
       <c r="F54" s="1" t="n">
-        <v>183.10347139069</v>
+        <v>237.251200595896</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
@@ -1566,10 +1566,10 @@
         <v>161.24032915439</v>
       </c>
       <c r="F55" s="1" t="n">
-        <v>180.822690385643</v>
+        <v>240.289460006464</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H55" s="1"/>
       <c r="I55" s="1"/>
@@ -1588,10 +1588,10 @@
         <v>163.640836796104</v>
       </c>
       <c r="F56" s="1" t="n">
-        <v>177.684923724264</v>
+        <v>242.238703075263</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -1610,10 +1610,10 @@
         <v>166.885766935062</v>
       </c>
       <c r="F57" s="1" t="n">
-        <v>172.135717838525</v>
+        <v>237.177618988262</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H57" s="1"/>
       <c r="I57" s="1"/>
@@ -1632,10 +1632,10 @@
         <v>167.674634796018</v>
       </c>
       <c r="F58" s="1" t="n">
-        <v>170.354593683038</v>
+        <v>232.868411232466</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H58" s="1"/>
       <c r="I58" s="1"/>
@@ -1654,10 +1654,10 @@
         <v>169.760812160816</v>
       </c>
       <c r="F59" s="1" t="n">
-        <v>163.954630270182</v>
+        <v>238.145401006412</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -1676,10 +1676,10 @@
         <v>170.043793662292</v>
       </c>
       <c r="F60" s="1" t="n">
-        <v>165.862808306931</v>
+        <v>236.679147429368</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
@@ -1698,10 +1698,10 @@
         <v>170.14564144976</v>
       </c>
       <c r="F61" s="1" t="n">
-        <v>168.312432893911</v>
+        <v>235.873116043294</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
@@ -1720,10 +1720,10 @@
         <v>169.718704482648</v>
       </c>
       <c r="F62" s="1" t="n">
-        <v>171.381985465375</v>
+        <v>234.731574748192</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H62" s="1"/>
       <c r="I62" s="1"/>
@@ -1742,10 +1742,10 @@
         <v>168.523192973369</v>
       </c>
       <c r="F63" s="1" t="n">
-        <v>174.154714506769</v>
+        <v>231.013300078218</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H63" s="1"/>
       <c r="I63" s="1"/>
@@ -1764,10 +1764,10 @@
         <v>166.958899850136</v>
       </c>
       <c r="F64" s="1" t="n">
-        <v>176.032679004596</v>
+        <v>225.550954502174</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -1786,10 +1786,10 @@
         <v>165.602418819852</v>
       </c>
       <c r="F65" s="1" t="n">
-        <v>177.085207810424</v>
+        <v>221.749682903928</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H65" s="1"/>
       <c r="I65" s="1"/>
@@ -1808,10 +1808,10 @@
         <v>163.985174178414</v>
       </c>
       <c r="F66" s="1" t="n">
-        <v>177.96411919758</v>
+        <v>221.606031980157</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H66" s="1"/>
       <c r="I66" s="1"/>
@@ -1830,10 +1830,10 @@
         <v>163.310178600558</v>
       </c>
       <c r="F67" s="1" t="n">
-        <v>178.246247023677</v>
+        <v>221.723876142886</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H67" s="1"/>
       <c r="I67" s="1"/>
@@ -1852,10 +1852,10 @@
         <v>162.512561053771</v>
       </c>
       <c r="F68" s="1" t="n">
-        <v>178.529113833608</v>
+        <v>222.060723474579</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
@@ -1874,10 +1874,10 @@
         <v>162.035898227893</v>
       </c>
       <c r="F69" s="1" t="n">
-        <v>178.675203922229</v>
+        <v>222.434560678118</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H69" s="1"/>
       <c r="I69" s="1"/>
@@ -1896,10 +1896,10 @@
         <v>152.602599805244</v>
       </c>
       <c r="F70" s="1" t="n">
-        <v>179.365651885185</v>
+        <v>223.882523509127</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H70" s="1"/>
       <c r="I70" s="1"/>
@@ -1918,10 +1918,10 @@
         <v>149.497767041358</v>
       </c>
       <c r="F71" s="1" t="n">
-        <v>179.006494789371</v>
+        <v>224.143316404604</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H71" s="1"/>
       <c r="I71" s="1"/>
@@ -1940,10 +1940,10 @@
         <v>146.119293519156</v>
       </c>
       <c r="F72" s="1" t="n">
-        <v>178.396895871301</v>
+        <v>224.717301658209</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H72" s="1"/>
       <c r="I72" s="1"/>
@@ -1962,10 +1962,10 @@
         <v>141.160912441675</v>
       </c>
       <c r="F73" s="1" t="n">
-        <v>177.159517399757</v>
+        <v>225.539284229366</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H73" s="1"/>
       <c r="I73" s="1"/>
@@ -1984,10 +1984,10 @@
         <v>138.474512285046</v>
       </c>
       <c r="F74" s="1" t="n">
-        <v>176.34152034447</v>
+        <v>225.973336527565</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H74" s="1"/>
       <c r="I74" s="1"/>
@@ -2006,10 +2006,10 @@
         <v>134.846113219079</v>
       </c>
       <c r="F75" s="1" t="n">
-        <v>175.089770928146</v>
+        <v>225.976963608325</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H75" s="1"/>
       <c r="I75" s="1"/>
@@ -2028,10 +2028,10 @@
         <v>132.224385504343</v>
       </c>
       <c r="F76" s="1" t="n">
-        <v>174.087371554148</v>
+        <v>225.389440592573</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H76" s="1"/>
       <c r="I76" s="1"/>
@@ -2050,10 +2050,10 @@
         <v>127.110019654785</v>
       </c>
       <c r="F77" s="1" t="n">
-        <v>171.911025769697</v>
+        <v>226.258894838464</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H77" s="1"/>
       <c r="I77" s="1"/>
@@ -2072,10 +2072,10 @@
         <v>122.145791477229</v>
       </c>
       <c r="F78" s="1" t="n">
-        <v>169.533511759582</v>
+        <v>223.296356414222</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
@@ -2094,10 +2094,10 @@
         <v>106.031671177383</v>
       </c>
       <c r="F79" s="1" t="n">
-        <v>160.081848785632</v>
+        <v>227.870951524246</v>
       </c>
       <c r="G79" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
@@ -2116,10 +2116,10 @@
         <v>100.56444829398</v>
       </c>
       <c r="F80" s="1" t="n">
-        <v>156.252742201839</v>
+        <v>227.737372818707</v>
       </c>
       <c r="G80" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H80" s="1"/>
       <c r="I80" s="1"/>
@@ -2138,10 +2138,10 @@
         <v>88.1140155361077</v>
       </c>
       <c r="F81" s="1" t="n">
-        <v>146.172621635447</v>
+        <v>230.269403226824</v>
       </c>
       <c r="G81" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H81" s="1"/>
       <c r="I81" s="1"/>
@@ -2160,10 +2160,10 @@
         <v>73.2545367299084</v>
       </c>
       <c r="F82" s="1" t="n">
-        <v>130.85224634782</v>
+        <v>231.480491775316</v>
       </c>
       <c r="G82" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H82" s="1"/>
       <c r="I82" s="1"/>
@@ -2182,10 +2182,10 @@
         <v>67.2932223653835</v>
       </c>
       <c r="F83" s="1" t="n">
-        <v>123.163051643273</v>
+        <v>227.107837199737</v>
       </c>
       <c r="G83" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H83" s="1"/>
       <c r="I83" s="1"/>
@@ -2204,10 +2204,10 @@
         <v>58.0666580441529</v>
       </c>
       <c r="F84" s="1" t="n">
-        <v>107.961782369297</v>
+        <v>213.489529669117</v>
       </c>
       <c r="G84" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H84" s="1"/>
       <c r="I84" s="1"/>
@@ -2226,10 +2226,10 @@
         <v>49.2672472996232</v>
       </c>
       <c r="F85" s="1" t="n">
-        <v>80.3737160856086</v>
+        <v>218.534055321096</v>
       </c>
       <c r="G85" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H85" s="1"/>
       <c r="I85" s="1"/>
@@ -2248,10 +2248,10 @@
         <v>48.5445964244528</v>
       </c>
       <c r="F86" s="1" t="n">
-        <v>71.9330249800469</v>
+        <v>222.646807898806</v>
       </c>
       <c r="G86" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H86" s="1"/>
       <c r="I86" s="1"/>
@@ -2270,10 +2270,10 @@
         <v>49.1880090563678</v>
       </c>
       <c r="F87" s="1" t="n">
-        <v>59.2924319174502</v>
+        <v>234.112479125131</v>
       </c>
       <c r="G87" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H87" s="1"/>
       <c r="I87" s="1"/>
@@ -2292,10 +2292,10 @@
         <v>56.2999282602716</v>
       </c>
       <c r="F88" s="1" t="n">
-        <v>37.1620579801267</v>
+        <v>220.557856955252</v>
       </c>
       <c r="G88" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H88" s="1"/>
       <c r="I88" s="1"/>
@@ -2314,10 +2314,10 @@
         <v>65.4856620232247</v>
       </c>
       <c r="F89" s="1" t="n">
-        <v>38.7429277279418</v>
+        <v>230.137121187121</v>
       </c>
       <c r="G89" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -2336,10 +2336,10 @@
         <v>93.3789751355505</v>
       </c>
       <c r="F90" s="1" t="n">
-        <v>56.1443033102909</v>
+        <v>217.151900862422</v>
       </c>
       <c r="G90" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
@@ -2358,10 +2358,10 @@
         <v>128.6206210176</v>
       </c>
       <c r="F91" s="1" t="n">
-        <v>90.5365198347471</v>
+        <v>221.309196030905</v>
       </c>
       <c r="G91" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H91" s="1"/>
       <c r="I91" s="1"/>
@@ -2380,10 +2380,10 @@
         <v>192.909339848763</v>
       </c>
       <c r="F92" s="1" t="n">
-        <v>140.368955968976</v>
+        <v>245.261078719406</v>
       </c>
       <c r="G92" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
@@ -2402,10 +2402,10 @@
         <v>349.212934580103</v>
       </c>
       <c r="F93" s="1" t="n">
-        <v>232.947761551038</v>
+        <v>226.597015345923</v>
       </c>
       <c r="G93" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H93" s="1"/>
       <c r="I93" s="1"/>
@@ -2424,10 +2424,10 @@
         <v>588.829995929074</v>
       </c>
       <c r="F94" s="1" t="n">
-        <v>228.745252125571</v>
+        <v>260.19281999265</v>
       </c>
       <c r="G94" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H94" s="1"/>
       <c r="I94" s="1"/>
@@ -2446,10 +2446,10 @@
         <v>1100.86042044384</v>
       </c>
       <c r="F95" s="1" t="n">
-        <v>369.300427877989</v>
+        <v>560.246305136283</v>
       </c>
       <c r="G95" s="1" t="n">
-        <v>12.9591133890607</v>
+        <v>2.27113200460251</v>
       </c>
       <c r="H95" s="1"/>
       <c r="I95" s="1"/>
